--- a/data-manipulation-scripts/sheets-cleanup/sheets/BUCHA QUADRO  08_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/BUCHA QUADRO  08_02.xlsx
@@ -52,7 +52,7 @@
     <t>7898590340063</t>
   </si>
   <si>
-    <t>BUCHA QUADRO VEDA+ CG TITAN 3005</t>
+    <t>BUCHA QUADRO PEÇA+ CG TITAN 3005</t>
   </si>
   <si>
     <t>7893986621931</t>
@@ -385,7 +385,9 @@
       <c r="C2" s="2">
         <v>2.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>18.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -397,7 +399,9 @@
       <c r="C3" s="2">
         <v>7.0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>30.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -409,7 +413,9 @@
       <c r="C4" s="2">
         <v>3.0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
@@ -421,7 +427,9 @@
       <c r="C5" s="2">
         <v>3.0</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="2">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -433,7 +441,9 @@
       <c r="C6" s="2">
         <v>3.0</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="2">
+        <v>30.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
@@ -445,7 +455,9 @@
       <c r="C7" s="2">
         <v>1.0</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="2">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
@@ -457,7 +469,9 @@
       <c r="C8" s="2">
         <v>1.0</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="2">
+        <v>25.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
@@ -469,7 +483,9 @@
       <c r="C9" s="2">
         <v>1.0</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="2">
+        <v>32.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
@@ -481,7 +497,9 @@
       <c r="C10" s="2">
         <v>3.0</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="2">
+        <v>30.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
